--- a/arduino_calibration/calibration_no_muxx/Strain Gauge Calibration.xlsx
+++ b/arduino_calibration/calibration_no_muxx/Strain Gauge Calibration.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/77ddd84a895fa801/Documents/UPenn/AWARE LAB/tetheredBalloon/arduino_calibration/calibration_no_muxx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58D27BC8-0B94-45D7-B8C0-8F76B831F062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{58D27BC8-0B94-45D7-B8C0-8F76B831F062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD1C5CD1-FE95-4669-A003-3A60EEA72108}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11860" xr2:uid="{0E4C5825-019B-4E7D-96D4-BC4C051785B4}"/>
+    <workbookView xWindow="-51720" yWindow="-3900" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{0E4C5825-019B-4E7D-96D4-BC4C051785B4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tether 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tether 0" sheetId="5" r:id="rId1"/>
+    <sheet name="Tether 1" sheetId="4" r:id="rId2"/>
+    <sheet name="Tether 2" sheetId="1" r:id="rId3"/>
+    <sheet name="Tether 3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,12 +42,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="3">
   <si>
     <t>Mass</t>
   </si>
   <si>
     <t>Reading</t>
+  </si>
+  <si>
+    <t>`</t>
   </si>
 </sst>
 </file>
@@ -138,9 +144,8 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> 1 Values</a:t>
+              <a:t> 0</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -184,11 +189,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Tether 1'!$B$1</c:f>
+              <c:f>'Tether 0'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Reading</c:v>
+                  <c:v>Mass</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -231,8 +236,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.11188320209973754"/>
-                  <c:y val="-0.58284922717993581"/>
+                  <c:x val="0.11479724409448819"/>
+                  <c:y val="-0.59148439778361039"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -267,120 +272,114 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'Tether 1'!$A$2:$A$20</c:f>
+              <c:f>'Tether 0'!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-398050</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>-397850.34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20</c:v>
+                  <c:v>-380990.41</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>-380980.16</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>30</c:v>
+                  <c:v>-369531.72</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>50</c:v>
+                  <c:v>-369672.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>50</c:v>
+                  <c:v>-349742.47</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>60</c:v>
+                  <c:v>-349767.72</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>60</c:v>
+                  <c:v>-337454.31</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>70</c:v>
+                  <c:v>-337413.53</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>70</c:v>
+                  <c:v>-329376.88</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>100</c:v>
+                  <c:v>-329772.81</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>100</c:v>
+                  <c:v>-301194.75</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-303023.03000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Tether 1'!$B$2:$B$20</c:f>
+              <c:f>'Tether 0'!$B$2:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>-244732.08</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-235211.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-235348.66</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-224016.91</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-226589.14</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-218073.5</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-219100.2</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-196514.23</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-197090.56</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-193245.91</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-193648.95</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-176852.63</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-176872.52</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-162246.34</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-162736.14000000001</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-146833.95000000001</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-146756.29999999999</c:v>
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -388,7 +387,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E7B4-442F-965A-DF6C5E81F2B6}"/>
+              <c16:uniqueId val="{00000001-8ADD-4240-BC50-7DFA9D7EFE5A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -400,13 +399,14 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1545579328"/>
-        <c:axId val="1379321328"/>
+        <c:axId val="1606398384"/>
+        <c:axId val="1555226000"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1545579328"/>
+        <c:axId val="1606398384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="-293023.03000000003"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -445,7 +445,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Mass (g)</a:t>
+                  <a:t>Raw Readings</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -516,12 +516,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1379321328"/>
+        <c:crossAx val="1555226000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1379321328"/>
+        <c:axId val="1555226000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -562,7 +562,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Raw Reading</a:t>
+                  <a:t>Mass (g)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -633,7 +633,1792 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1545579328"/>
+        <c:crossAx val="1606398384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>SG</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> 1</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Tether 1'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mass</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.11073578302712161"/>
+                  <c:y val="-0.52094233012540103"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Tether 1'!$A$2:$A$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>456843.72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>456857.78</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>467657.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>467622.06</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>471518.03</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>471554.63</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>482639.41</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>482606.25</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>509971.91</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>509551.31</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>516754.28</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>516594.19</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>525130.56000000006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>525377.81000000006</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>534390.93999999994</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>534312.06000000006</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>552224.06000000006</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>548369.56000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Tether 1'!$B$2:$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FCE8-4C99-B82D-06E6F712FD01}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1606398384"/>
+        <c:axId val="1555226000"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1606398384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="450000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Raw Readings</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1555226000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1555226000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Mass (g)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1606398384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>SG 2</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Tether 2'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mass</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.39729724409448819"/>
+                  <c:y val="-0.19015857392825897"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Tether 2'!$A$2:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>-244732.08</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-235211.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-235348.66</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-224016.91</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-226589.14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-218073.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-219100.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-196514.23</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-197090.56</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-193245.91</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-193648.95</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-176852.63</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-176872.52</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-162246.34</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-162736.14000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-146833.95000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-146756.29999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Tether 2'!$B$2:$B$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BBF3-4051-ABA6-FEC0B5B631E7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1606398384"/>
+        <c:axId val="1555226000"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1606398384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="-100000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Raw</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Readings</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1555226000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1555226000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Mass (g)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1606398384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>SG</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> 3</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Tether 3'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mass</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.39729724409448819"/>
+                  <c:y val="-0.19015857392825897"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Tether 3'!$A$2:$A$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>-317041.28000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-317014.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-312228.96999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-312342.46999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-300679.25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-300534.21999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-297519.59000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-297397.63</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-270851.46999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-270972.38</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-263244.84000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-263345.75</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-249183.69</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-249183.69</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-237096.06</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-237007.05</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-219714.06</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-219308.83</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Tether 3'!$B$2:$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7C4C-4540-ACD2-8E26D33C955D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1606398384"/>
+        <c:axId val="1555226000"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1606398384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="-200000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Raw Readings</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1555226000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1555226000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Mass (g)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1606398384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -729,6 +2514,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1245,27 +3150,1661 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>536575</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>587375</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>231775</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>282575</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A23619E6-EF47-D03F-EBAB-C1489A7301C3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{807D048B-610C-4CA5-ACA8-31323622AD09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>587375</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>282575</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A6D0879-82D8-47BD-824B-0BE47B2AE78D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>587375</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>282575</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76644A4D-FC19-103C-F8BF-550BB4C6C071}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1284,6 +4823,53 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>587375</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>282575</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F891F9D5-2B6D-4800-8505-20D29A04C31A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1602,152 +5188,641 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2DB1ACB-6500-4F6C-8FEE-8827839F6DFF}">
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>-398050</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>-397850.34</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>-380990.41</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>-380980.16</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>-369531.72</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>-369672.25</v>
+      </c>
+      <c r="B9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>-349742.47</v>
+      </c>
+      <c r="B10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>-349767.72</v>
+      </c>
+      <c r="B11">
+        <v>50</v>
+      </c>
+      <c r="M11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>-337454.31</v>
+      </c>
+      <c r="B12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>-337413.53</v>
+      </c>
+      <c r="B13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>-329376.88</v>
+      </c>
+      <c r="B14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>-329772.81</v>
+      </c>
+      <c r="B15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>-301194.75</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>-303023.03000000003</v>
+      </c>
+      <c r="B19">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{577810B9-01F6-43AA-B48A-11CBC02F88AE}">
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>456843.72</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>456857.78</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>467657.75</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>467622.06</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>471518.03</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>471554.63</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>482639.41</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>482606.25</v>
+      </c>
+      <c r="B9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>509971.91</v>
+      </c>
+      <c r="B10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>509551.31</v>
+      </c>
+      <c r="B11">
+        <v>50</v>
+      </c>
+      <c r="M11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>516754.28</v>
+      </c>
+      <c r="B12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>516594.19</v>
+      </c>
+      <c r="B13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>525130.56000000006</v>
+      </c>
+      <c r="B14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>525377.81000000006</v>
+      </c>
+      <c r="B15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>534390.93999999994</v>
+      </c>
+      <c r="B16">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>534312.06000000006</v>
+      </c>
+      <c r="B17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>552224.06000000006</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>548369.56000000006</v>
+      </c>
+      <c r="B19">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DAA7F3C-2783-47CA-B067-3205FC8383DA}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>-244732.08</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>-235211.2</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>-235348.66</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>-224016.91</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>-226589.14</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>-218073.5</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>-219100.2</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>-196514.23</v>
+      </c>
+      <c r="B9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>-197090.56</v>
+      </c>
+      <c r="B10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>-193245.91</v>
+      </c>
+      <c r="B11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>-193648.95</v>
+      </c>
+      <c r="B12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>-176852.63</v>
+      </c>
+      <c r="B13">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>-176872.52</v>
+      </c>
+      <c r="B14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>-162246.34</v>
+      </c>
+      <c r="B15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>-162736.14000000001</v>
+      </c>
+      <c r="B16">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>-146833.95000000001</v>
+      </c>
+      <c r="B17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>-146756.29999999999</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644AA01A-DF58-4E46-98A1-590BCFDB8F29}">
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>-317041.28000000003</v>
+      </c>
+      <c r="B2">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>-244732.08</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>-317014.75</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>-312228.96999999997</v>
+      </c>
+      <c r="B4">
         <v>10</v>
       </c>
-      <c r="B3">
-        <v>-235211.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>-312342.46999999997</v>
+      </c>
+      <c r="B5">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>-235348.66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>-300679.25</v>
+      </c>
+      <c r="B6">
         <v>20</v>
       </c>
-      <c r="B5">
-        <v>-224016.91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6">
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>-300534.21999999997</v>
+      </c>
+      <c r="B7">
         <v>20</v>
       </c>
-      <c r="B6">
-        <v>-226589.14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7">
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>-297519.59000000003</v>
+      </c>
+      <c r="B8">
         <v>30</v>
       </c>
-      <c r="B7">
-        <v>-218073.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8">
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>-297397.63</v>
+      </c>
+      <c r="B9">
         <v>30</v>
       </c>
-      <c r="B8">
-        <v>-219100.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9">
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>-270851.46999999997</v>
+      </c>
+      <c r="B10">
         <v>50</v>
       </c>
-      <c r="B9">
-        <v>-196514.23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10">
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>-270972.38</v>
+      </c>
+      <c r="B11">
         <v>50</v>
       </c>
-      <c r="B10">
-        <v>-197090.56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="M11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>-263244.84000000003</v>
+      </c>
+      <c r="B12">
         <v>60</v>
       </c>
-      <c r="B11">
-        <v>-193245.91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12">
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>-263345.75</v>
+      </c>
+      <c r="B13">
         <v>60</v>
       </c>
-      <c r="B12">
-        <v>-193648.95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13">
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>-249183.69</v>
+      </c>
+      <c r="B14">
         <v>70</v>
       </c>
-      <c r="B13">
-        <v>-176852.63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14">
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>-249183.69</v>
+      </c>
+      <c r="B15">
         <v>70</v>
       </c>
-      <c r="B14">
-        <v>-176872.52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15">
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>-237096.06</v>
+      </c>
+      <c r="B16">
         <v>80</v>
       </c>
-      <c r="B15">
-        <v>-162246.34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>-237007.05</v>
+      </c>
+      <c r="B17">
         <v>80</v>
       </c>
-      <c r="B16">
-        <v>-162736.14000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>-219714.06</v>
+      </c>
+      <c r="B18">
         <v>100</v>
       </c>
-      <c r="B17">
-        <v>-146833.95000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>-219308.83</v>
+      </c>
+      <c r="B19">
         <v>100</v>
-      </c>
-      <c r="B18">
-        <v>-146756.29999999999</v>
       </c>
     </row>
   </sheetData>

--- a/arduino_calibration/calibration_no_muxx/Strain Gauge Calibration.xlsx
+++ b/arduino_calibration/calibration_no_muxx/Strain Gauge Calibration.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/77ddd84a895fa801/Documents/UPenn/AWARE LAB/tetheredBalloon/arduino_calibration/calibration_no_muxx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/10f97b7a6f37ab84/Documents/GitHub/tetheredBalloon/arduino_calibration/calibration_no_muxx/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="176" documentId="8_{58D27BC8-0B94-45D7-B8C0-8F76B831F062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD1C5CD1-FE95-4669-A003-3A60EEA72108}"/>
   <bookViews>
-    <workbookView xWindow="-51720" yWindow="-3900" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{0E4C5825-019B-4E7D-96D4-BC4C051785B4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{0E4C5825-019B-4E7D-96D4-BC4C051785B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tether 0" sheetId="5" r:id="rId1"/>
@@ -4868,10 +4868,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5190,9 +5186,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2DB1ACB-6500-4F6C-8FEE-8827839F6DFF}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -5200,7 +5196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>-398050</v>
       </c>
@@ -5208,7 +5204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>-397850.34</v>
       </c>
@@ -5216,17 +5212,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>-380990.41</v>
       </c>
@@ -5234,7 +5230,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>-380980.16</v>
       </c>
@@ -5242,7 +5238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>-369531.72</v>
       </c>
@@ -5250,7 +5246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>-369672.25</v>
       </c>
@@ -5258,7 +5254,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-349742.47</v>
       </c>
@@ -5266,7 +5262,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-349767.72</v>
       </c>
@@ -5277,7 +5273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-337454.31</v>
       </c>
@@ -5285,7 +5281,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-337413.53</v>
       </c>
@@ -5293,7 +5289,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-329376.88</v>
       </c>
@@ -5301,7 +5297,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-329772.81</v>
       </c>
@@ -5309,17 +5305,17 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>-301194.75</v>
       </c>
@@ -5327,7 +5323,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>-303023.03000000003</v>
       </c>
@@ -5345,9 +5341,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{577810B9-01F6-43AA-B48A-11CBC02F88AE}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -5355,7 +5351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>456843.72</v>
       </c>
@@ -5363,7 +5359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>456857.78</v>
       </c>
@@ -5371,7 +5367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>467657.75</v>
       </c>
@@ -5379,7 +5375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>467622.06</v>
       </c>
@@ -5387,7 +5383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>471518.03</v>
       </c>
@@ -5395,7 +5391,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>471554.63</v>
       </c>
@@ -5403,7 +5399,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>482639.41</v>
       </c>
@@ -5411,7 +5407,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>482606.25</v>
       </c>
@@ -5419,7 +5415,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>509971.91</v>
       </c>
@@ -5427,7 +5423,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>509551.31</v>
       </c>
@@ -5438,7 +5434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>516754.28</v>
       </c>
@@ -5446,7 +5442,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>516594.19</v>
       </c>
@@ -5454,7 +5450,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>525130.56000000006</v>
       </c>
@@ -5462,7 +5458,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>525377.81000000006</v>
       </c>
@@ -5470,7 +5466,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>534390.93999999994</v>
       </c>
@@ -5478,7 +5474,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>534312.06000000006</v>
       </c>
@@ -5486,7 +5482,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>552224.06000000006</v>
       </c>
@@ -5494,7 +5490,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>548369.56000000006</v>
       </c>
@@ -5512,9 +5508,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DAA7F3C-2783-47CA-B067-3205FC8383DA}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -5522,7 +5518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>-244732.08</v>
       </c>
@@ -5530,7 +5526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>-235211.2</v>
       </c>
@@ -5538,7 +5534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>-235348.66</v>
       </c>
@@ -5546,7 +5542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>-224016.91</v>
       </c>
@@ -5554,7 +5550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>-226589.14</v>
       </c>
@@ -5562,7 +5558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>-218073.5</v>
       </c>
@@ -5570,7 +5566,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>-219100.2</v>
       </c>
@@ -5578,7 +5574,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>-196514.23</v>
       </c>
@@ -5586,7 +5582,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-197090.56</v>
       </c>
@@ -5594,7 +5590,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-193245.91</v>
       </c>
@@ -5602,7 +5598,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-193648.95</v>
       </c>
@@ -5610,7 +5606,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-176852.63</v>
       </c>
@@ -5618,7 +5614,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-176872.52</v>
       </c>
@@ -5626,7 +5622,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-162246.34</v>
       </c>
@@ -5634,7 +5630,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>-162736.14000000001</v>
       </c>
@@ -5642,7 +5638,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>-146833.95000000001</v>
       </c>
@@ -5650,7 +5646,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>-146756.29999999999</v>
       </c>
@@ -5668,9 +5664,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644AA01A-DF58-4E46-98A1-590BCFDB8F29}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -5678,7 +5674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>-317041.28000000003</v>
       </c>
@@ -5686,7 +5682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>-317014.75</v>
       </c>
@@ -5694,7 +5690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>-312228.96999999997</v>
       </c>
@@ -5702,7 +5698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>-312342.46999999997</v>
       </c>
@@ -5710,7 +5706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>-300679.25</v>
       </c>
@@ -5718,7 +5714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>-300534.21999999997</v>
       </c>
@@ -5726,7 +5722,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>-297519.59000000003</v>
       </c>
@@ -5734,7 +5730,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>-297397.63</v>
       </c>
@@ -5742,7 +5738,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-270851.46999999997</v>
       </c>
@@ -5750,7 +5746,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-270972.38</v>
       </c>
@@ -5761,7 +5757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-263244.84000000003</v>
       </c>
@@ -5769,7 +5765,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-263345.75</v>
       </c>
@@ -5777,7 +5773,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-249183.69</v>
       </c>
@@ -5785,7 +5781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-249183.69</v>
       </c>
@@ -5793,7 +5789,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>-237096.06</v>
       </c>
@@ -5801,7 +5797,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>-237007.05</v>
       </c>
@@ -5809,7 +5805,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>-219714.06</v>
       </c>
@@ -5817,7 +5813,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>-219308.83</v>
       </c>
